--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -229,6 +229,12 @@
   </si>
   <si>
     <t>Stressed</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>listened music</t>
   </si>
 </sst>
 </file>
@@ -2158,26 +2164,50 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13" t="str">
+      <c r="A22" s="11">
+        <v>46256</v>
+      </c>
+      <c r="B22" s="12">
+        <v>450</v>
+      </c>
+      <c r="C22" s="12">
+        <v>5</v>
+      </c>
+      <c r="D22" s="12">
+        <v>60</v>
+      </c>
+      <c r="E22" s="12">
+        <v>10</v>
+      </c>
+      <c r="F22" s="12">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12">
+        <v>0</v>
+      </c>
+      <c r="H22" s="12">
+        <v>20</v>
+      </c>
+      <c r="I22" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="13" t="str">
+        <v>545</v>
+      </c>
+      <c r="J22" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="15"/>
+        <v>895</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="23" spans="1:14">
       <c r="A23" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6910" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>listened music</t>
+  </si>
+  <si>
+    <t>focused on studies</t>
   </si>
 </sst>
 </file>
@@ -2210,26 +2213,50 @@
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13" t="str">
+      <c r="A23" s="11">
+        <v>46257</v>
+      </c>
+      <c r="B23" s="12">
+        <v>350</v>
+      </c>
+      <c r="C23" s="12">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12">
+        <v>120</v>
+      </c>
+      <c r="E23" s="12">
+        <v>30</v>
+      </c>
+      <c r="F23" s="12">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12">
+        <v>0</v>
+      </c>
+      <c r="H23" s="12">
+        <v>10</v>
+      </c>
+      <c r="I23" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="13" t="str">
+        <v>510</v>
+      </c>
+      <c r="J23" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="15"/>
+        <v>930</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N23" s="15" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="24" spans="1:14">
       <c r="A24" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,12 @@
   </si>
   <si>
     <t>focused on studies</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Good mood</t>
   </si>
 </sst>
 </file>
@@ -2259,26 +2265,50 @@
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13" t="str">
+      <c r="A24" s="11">
+        <v>46258</v>
+      </c>
+      <c r="B24" s="12">
+        <v>374</v>
+      </c>
+      <c r="C24" s="12">
+        <v>12</v>
+      </c>
+      <c r="D24" s="12">
+        <v>60</v>
+      </c>
+      <c r="E24" s="12">
+        <v>10</v>
+      </c>
+      <c r="F24" s="12">
+        <v>200</v>
+      </c>
+      <c r="G24" s="12">
+        <v>4</v>
+      </c>
+      <c r="H24" s="12">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="13" t="str">
+        <v>656</v>
+      </c>
+      <c r="J24" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="15"/>
+        <v>784</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N24" s="15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" spans="1:14">
       <c r="A25" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2311,26 +2311,50 @@
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13" t="str">
+      <c r="A25" s="11">
+        <v>46259</v>
+      </c>
+      <c r="B25" s="12">
+        <v>400</v>
+      </c>
+      <c r="C25" s="12">
+        <v>10</v>
+      </c>
+      <c r="D25" s="12">
+        <v>60</v>
+      </c>
+      <c r="E25" s="12">
+        <v>60</v>
+      </c>
+      <c r="F25" s="12">
+        <v>250</v>
+      </c>
+      <c r="G25" s="12">
+        <v>5</v>
+      </c>
+      <c r="H25" s="12">
+        <v>30</v>
+      </c>
+      <c r="I25" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="13" t="str">
+        <v>810</v>
+      </c>
+      <c r="J25" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15"/>
+        <v>630</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L25" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="15" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="26" spans="1:14">
       <c r="A26" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6910" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>Good mood</t>
+  </si>
+  <si>
+    <t>watched a movie</t>
   </si>
 </sst>
 </file>
@@ -2357,26 +2360,50 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="13" t="str">
+      <c r="A26" s="11">
+        <v>46260</v>
+      </c>
+      <c r="B26" s="12">
+        <v>300</v>
+      </c>
+      <c r="C26" s="12">
+        <v>50</v>
+      </c>
+      <c r="D26" s="12">
+        <v>100</v>
+      </c>
+      <c r="E26" s="12">
+        <v>50</v>
+      </c>
+      <c r="F26" s="12">
+        <v>250</v>
+      </c>
+      <c r="G26" s="12">
+        <v>5</v>
+      </c>
+      <c r="H26" s="12">
+        <v>40</v>
+      </c>
+      <c r="I26" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="13" t="str">
+        <v>790</v>
+      </c>
+      <c r="J26" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="15"/>
+        <v>650</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L26" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="15" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6910" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="13120" windowHeight="7180" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>watched a movie</t>
+  </si>
+  <si>
+    <t>Got a new friend</t>
   </si>
 </sst>
 </file>
@@ -2406,26 +2409,50 @@
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13" t="str">
+      <c r="A27" s="11">
+        <v>46261</v>
+      </c>
+      <c r="B27" s="12">
+        <v>400</v>
+      </c>
+      <c r="C27" s="12">
+        <v>70</v>
+      </c>
+      <c r="D27" s="12">
+        <v>50</v>
+      </c>
+      <c r="E27" s="12">
+        <v>30</v>
+      </c>
+      <c r="F27" s="12">
+        <v>300</v>
+      </c>
+      <c r="G27" s="12">
+        <v>6</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="13" t="str">
+        <v>850</v>
+      </c>
+      <c r="J27" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="15"/>
+        <v>590</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L27" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N27" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>Got a new friend</t>
+  </si>
+  <si>
+    <t>Celebrated Rakhi</t>
   </si>
 </sst>
 </file>
@@ -2455,26 +2458,44 @@
       </c>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="11"/>
+      <c r="A28" s="11">
+        <v>46262</v>
+      </c>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="13" t="str">
+      <c r="E28" s="12">
+        <v>0</v>
+      </c>
+      <c r="F28" s="12">
+        <v>200</v>
+      </c>
+      <c r="G28" s="12">
+        <v>4</v>
+      </c>
+      <c r="H28" s="12">
+        <v>120</v>
+      </c>
+      <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="13" t="str">
+        <v>320</v>
+      </c>
+      <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-      <c r="N28" s="15"/>
+        <v>1120</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L28" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N28" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2461,9 +2461,15 @@
       <c r="A28" s="11">
         <v>46262</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
+      <c r="B28" s="12">
+        <v>500</v>
+      </c>
+      <c r="C28" s="12">
+        <v>30</v>
+      </c>
+      <c r="D28" s="12">
+        <v>70</v>
+      </c>
       <c r="E28" s="12">
         <v>0</v>
       </c>
@@ -2478,11 +2484,11 @@
       </c>
       <c r="I28" s="13">
         <f t="shared" si="0"/>
-        <v>320</v>
+        <v>920</v>
       </c>
       <c r="J28" s="13">
         <f t="shared" si="1"/>
-        <v>1120</v>
+        <v>520</v>
       </c>
       <c r="K28" s="14" t="s">
         <v>67</v>
@@ -2498,26 +2504,50 @@
       </c>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13" t="str">
+      <c r="A29" s="11">
+        <v>46263</v>
+      </c>
+      <c r="B29" s="12">
+        <v>500</v>
+      </c>
+      <c r="C29" s="12">
+        <v>50</v>
+      </c>
+      <c r="D29" s="12">
+        <v>70</v>
+      </c>
+      <c r="E29" s="12">
+        <v>100</v>
+      </c>
+      <c r="F29" s="12">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12">
+        <v>0</v>
+      </c>
+      <c r="H29" s="12">
+        <v>60</v>
+      </c>
+      <c r="I29" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="13" t="str">
+        <v>780</v>
+      </c>
+      <c r="J29" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="15"/>
+        <v>660</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="15" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="13120" windowHeight="7180" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -253,6 +253,9 @@
   </si>
   <si>
     <t>Celebrated Rakhi</t>
+  </si>
+  <si>
+    <t>watched  anime</t>
   </si>
 </sst>
 </file>
@@ -2550,26 +2553,50 @@
       </c>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13" t="str">
+      <c r="A30" s="11">
+        <v>46264</v>
+      </c>
+      <c r="B30" s="12">
+        <v>480</v>
+      </c>
+      <c r="C30" s="12">
+        <v>60</v>
+      </c>
+      <c r="D30" s="12">
+        <v>120</v>
+      </c>
+      <c r="E30" s="12">
+        <v>100</v>
+      </c>
+      <c r="F30" s="12">
+        <v>100</v>
+      </c>
+      <c r="G30" s="12">
+        <v>2</v>
+      </c>
+      <c r="H30" s="12">
+        <v>50</v>
+      </c>
+      <c r="I30" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="13" t="str">
+        <v>910</v>
+      </c>
+      <c r="J30" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="15"/>
+        <v>530</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L30" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="15" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -256,6 +256,9 @@
   </si>
   <si>
     <t>watched  anime</t>
+  </si>
+  <si>
+    <t>Health down</t>
   </si>
 </sst>
 </file>
@@ -2569,21 +2572,21 @@
         <v>100</v>
       </c>
       <c r="F30" s="12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G30" s="12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="12">
         <v>50</v>
       </c>
       <c r="I30" s="13">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>810</v>
       </c>
       <c r="J30" s="13">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>630</v>
       </c>
       <c r="K30" s="14" t="s">
         <v>53</v>
@@ -2599,26 +2602,50 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="13" t="str">
+      <c r="A31" s="11">
+        <v>46265</v>
+      </c>
+      <c r="B31" s="12">
+        <v>400</v>
+      </c>
+      <c r="C31" s="12">
+        <v>60</v>
+      </c>
+      <c r="D31" s="12">
+        <v>60</v>
+      </c>
+      <c r="E31" s="12">
+        <v>60</v>
+      </c>
+      <c r="F31" s="12">
+        <v>100</v>
+      </c>
+      <c r="G31" s="12">
+        <v>2</v>
+      </c>
+      <c r="H31" s="12">
+        <v>80</v>
+      </c>
+      <c r="I31" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="13" t="str">
+        <v>760</v>
+      </c>
+      <c r="J31" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-      <c r="N31" s="15"/>
+        <v>680</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M31" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="15" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Health down</t>
+  </si>
+  <si>
+    <t>Got fever</t>
   </si>
 </sst>
 </file>
@@ -2648,26 +2651,50 @@
       </c>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="13" t="str">
+      <c r="A32" s="11">
+        <v>46266</v>
+      </c>
+      <c r="B32" s="12">
+        <v>410</v>
+      </c>
+      <c r="C32" s="12">
+        <v>60</v>
+      </c>
+      <c r="D32" s="12">
+        <v>200</v>
+      </c>
+      <c r="E32" s="12">
+        <v>100</v>
+      </c>
+      <c r="F32" s="12">
+        <v>250</v>
+      </c>
+      <c r="G32" s="12">
+        <v>5</v>
+      </c>
+      <c r="H32" s="12">
+        <v>70</v>
+      </c>
+      <c r="I32" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="13" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J32" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="15"/>
+        <v>350</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M32" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N32" s="15" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -262,6 +262,9 @@
   </si>
   <si>
     <t>Got fever</t>
+  </si>
+  <si>
+    <t>Focus on python study</t>
   </si>
 </sst>
 </file>
@@ -2697,26 +2700,50 @@
       </c>
     </row>
     <row r="33" spans="1:14">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13" t="str">
+      <c r="A33" s="11">
+        <v>46267</v>
+      </c>
+      <c r="B33" s="12">
+        <v>390</v>
+      </c>
+      <c r="C33" s="12">
+        <v>50</v>
+      </c>
+      <c r="D33" s="12">
+        <v>50</v>
+      </c>
+      <c r="E33" s="12">
+        <v>20</v>
+      </c>
+      <c r="F33" s="12">
+        <v>250</v>
+      </c>
+      <c r="G33" s="12">
+        <v>5</v>
+      </c>
+      <c r="H33" s="12">
+        <v>100</v>
+      </c>
+      <c r="I33" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="13" t="str">
+        <v>860</v>
+      </c>
+      <c r="J33" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="15"/>
+        <v>580</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7510" tabRatio="500" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6310" tabRatio="500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>Focus on python study</t>
+  </si>
+  <si>
+    <t>Revision day</t>
   </si>
 </sst>
 </file>
@@ -2746,26 +2749,50 @@
       </c>
     </row>
     <row r="34" spans="1:14">
-      <c r="A34" s="11"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="13" t="str">
+      <c r="A34" s="11">
+        <v>46268</v>
+      </c>
+      <c r="B34" s="12">
+        <v>400</v>
+      </c>
+      <c r="C34" s="12">
+        <v>100</v>
+      </c>
+      <c r="D34" s="12">
+        <v>180</v>
+      </c>
+      <c r="E34" s="12">
+        <v>60</v>
+      </c>
+      <c r="F34" s="12">
+        <v>300</v>
+      </c>
+      <c r="G34" s="12">
+        <v>6</v>
+      </c>
+      <c r="H34" s="12">
+        <v>45</v>
+      </c>
+      <c r="I34" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="13" t="str">
+        <v>1085</v>
+      </c>
+      <c r="J34" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="15"/>
+        <v>355</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M34" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="15" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -268,6 +268,9 @@
   </si>
   <si>
     <t>Revision day</t>
+  </si>
+  <si>
+    <t>Revised DBMS Keys</t>
   </si>
 </sst>
 </file>
@@ -2795,26 +2798,50 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="11"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13" t="str">
+      <c r="A35" s="11">
+        <v>46269</v>
+      </c>
+      <c r="B35" s="12">
+        <v>350</v>
+      </c>
+      <c r="C35" s="12">
+        <v>20</v>
+      </c>
+      <c r="D35" s="12">
+        <v>200</v>
+      </c>
+      <c r="E35" s="12">
+        <v>20</v>
+      </c>
+      <c r="F35" s="12">
+        <v>350</v>
+      </c>
+      <c r="G35" s="12">
+        <v>7</v>
+      </c>
+      <c r="H35" s="12">
+        <v>80</v>
+      </c>
+      <c r="I35" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="13" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-      <c r="N35" s="15"/>
+        <v>420</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L35" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -271,6 +271,9 @@
   </si>
   <si>
     <t>Revised DBMS Keys</t>
+  </si>
+  <si>
+    <t>Practiced arrays</t>
   </si>
 </sst>
 </file>
@@ -2814,21 +2817,21 @@
         <v>20</v>
       </c>
       <c r="F35" s="12">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G35" s="12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H35" s="12">
         <v>80</v>
       </c>
       <c r="I35" s="13">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>970</v>
       </c>
       <c r="J35" s="13">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>470</v>
       </c>
       <c r="K35" s="14" t="s">
         <v>62</v>
@@ -2844,26 +2847,50 @@
       </c>
     </row>
     <row r="36" spans="1:14">
-      <c r="A36" s="11"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="13" t="str">
+      <c r="A36" s="11">
+        <v>46270</v>
+      </c>
+      <c r="B36" s="12">
+        <v>320</v>
+      </c>
+      <c r="C36" s="12">
+        <v>50</v>
+      </c>
+      <c r="D36" s="12">
+        <v>120</v>
+      </c>
+      <c r="E36" s="12">
+        <v>78</v>
+      </c>
+      <c r="F36" s="12">
+        <v>350</v>
+      </c>
+      <c r="G36" s="12">
+        <v>7</v>
+      </c>
+      <c r="H36" s="12">
+        <v>100</v>
+      </c>
+      <c r="I36" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="13" t="str">
+        <v>1018</v>
+      </c>
+      <c r="J36" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="15"/>
+        <v>422</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="N36" s="15" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -274,6 +274,9 @@
   </si>
   <si>
     <t>Practiced arrays</t>
+  </si>
+  <si>
+    <t>Prepared for CA</t>
   </si>
 </sst>
 </file>
@@ -2863,21 +2866,21 @@
         <v>78</v>
       </c>
       <c r="F36" s="12">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="G36" s="12">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H36" s="12">
         <v>100</v>
       </c>
       <c r="I36" s="13">
         <f t="shared" si="0"/>
-        <v>1018</v>
+        <v>668</v>
       </c>
       <c r="J36" s="13">
         <f t="shared" si="1"/>
-        <v>422</v>
+        <v>772</v>
       </c>
       <c r="K36" s="14" t="s">
         <v>53</v>
@@ -2893,26 +2896,50 @@
       </c>
     </row>
     <row r="37" spans="1:14">
-      <c r="A37" s="11"/>
-      <c r="B37" s="12"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="13" t="str">
+      <c r="A37" s="11">
+        <v>46271</v>
+      </c>
+      <c r="B37" s="12">
+        <v>400</v>
+      </c>
+      <c r="C37" s="12">
+        <v>60</v>
+      </c>
+      <c r="D37" s="12">
+        <v>120</v>
+      </c>
+      <c r="E37" s="12">
+        <v>60</v>
+      </c>
+      <c r="F37" s="12">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12">
+        <v>0</v>
+      </c>
+      <c r="H37" s="12">
+        <v>50</v>
+      </c>
+      <c r="I37" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="13" t="str">
+        <v>690</v>
+      </c>
+      <c r="J37" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="15"/>
+        <v>750</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2942,26 +2942,50 @@
       </c>
     </row>
     <row r="38" spans="1:14">
-      <c r="A38" s="11"/>
-      <c r="B38" s="12"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="13" t="str">
+      <c r="A38" s="11">
+        <v>46272</v>
+      </c>
+      <c r="B38" s="12">
+        <v>400</v>
+      </c>
+      <c r="C38" s="12">
+        <v>40</v>
+      </c>
+      <c r="D38" s="12">
+        <v>50</v>
+      </c>
+      <c r="E38" s="12">
+        <v>30</v>
+      </c>
+      <c r="F38" s="12">
+        <v>250</v>
+      </c>
+      <c r="G38" s="12">
+        <v>5</v>
+      </c>
+      <c r="H38" s="12">
+        <v>200</v>
+      </c>
+      <c r="I38" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="13" t="str">
+        <v>970</v>
+      </c>
+      <c r="J38" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="15"/>
+        <v>470</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="M38" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="15" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" s="11"/>

--- a/12624438.xlsx
+++ b/12624438.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2988,26 +2988,50 @@
       </c>
     </row>
     <row r="39" spans="1:14">
-      <c r="A39" s="11"/>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="13" t="str">
+      <c r="A39" s="11">
+        <v>46273</v>
+      </c>
+      <c r="B39" s="12">
+        <v>350</v>
+      </c>
+      <c r="C39" s="12">
+        <v>40</v>
+      </c>
+      <c r="D39" s="12">
+        <v>100</v>
+      </c>
+      <c r="E39" s="12">
+        <v>70</v>
+      </c>
+      <c r="F39" s="12">
+        <v>250</v>
+      </c>
+      <c r="G39" s="12">
+        <v>5</v>
+      </c>
+      <c r="H39" s="12">
+        <v>120</v>
+      </c>
+      <c r="I39" s="13">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="13" t="str">
+        <v>930</v>
+      </c>
+      <c r="J39" s="13">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="14"/>
-      <c r="N39" s="15"/>
+        <v>510</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="M39" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="N39" s="15" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="11"/>
